--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487445_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487445_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.603199999999999</v>
+        <v>8.4261</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7105</v>
+        <v>7.2551</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8928</v>
+        <v>1.171</v>
       </c>
       <c r="G2" t="n">
         <v>3.6849</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2529</v>
+        <v>3.0758</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9951</v>
+        <v>1.5397</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2578</v>
+        <v>1.5361</v>
       </c>
       <c r="V2" t="n">
         <v>0.09859999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9631</v>
+        <v>2.5712</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0826</v>
+        <v>1.3164</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8804999999999999</v>
+        <v>1.2548</v>
       </c>
       <c r="G3" t="n">
         <v>-2.5784</v>
@@ -688,13 +688,13 @@
         <v>1.5668</v>
       </c>
       <c r="S3" t="n">
-        <v>4.6928</v>
+        <v>3.3009</v>
       </c>
       <c r="T3" t="n">
-        <v>4.2169</v>
+        <v>2.4508</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4759</v>
+        <v>0.8502</v>
       </c>
       <c r="V3" t="n">
         <v>3.4155</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. LATAS CHICO</t>
+          <t>J. ABELLEIRA MARTINEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8567</v>
+        <v>1.2908</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7421</v>
+        <v>-1.0378</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5988</v>
+        <v>2.3286</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.19</v>
+        <v>-1.0473</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1807</v>
+        <v>-1.2045</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9907</v>
+        <v>0.1572</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.016</v>
+        <v>0.4673</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7079</v>
+        <v>-0.1889</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6919</v>
+        <v>0.6563</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.174</v>
+        <v>-1.5146</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4729</v>
+        <v>-1.0156</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2988</v>
+        <v>-0.4991</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9792</v>
+        <v>-2.1543</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1336</v>
+        <v>-5.0921</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1543</v>
+        <v>2.9377</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8657</v>
+        <v>2.8442</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2473</v>
+        <v>1.762</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6185</v>
+        <v>1.0822</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1602</v>
+        <v>1.6482</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1602</v>
+        <v>1.8249</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1767</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>M. LATAS CHICO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0417</v>
+        <v>1.1673</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5634</v>
+        <v>-1.4849</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4783</v>
+        <v>2.6523</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3416</v>
+        <v>-0.19</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0677</v>
+        <v>-1.1807</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4093</v>
+        <v>0.9907</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0.016</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.7079</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.6919</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3416</v>
+        <v>-0.174</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0677</v>
+        <v>-0.4729</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4093</v>
+        <v>0.2988</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1958</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.1336</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1958</v>
+        <v>2.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5042</v>
+        <v>2.1764</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5634</v>
+        <v>1.5044</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0592</v>
+        <v>0.672</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1602</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1602</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0137</v>
+        <v>1.132</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2344</v>
+        <v>0.6172</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2207</v>
+        <v>0.5148</v>
       </c>
       <c r="G6" t="n">
         <v>-2.2815</v>
@@ -922,13 +922,13 @@
         <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9698</v>
+        <v>3.1155</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3274</v>
+        <v>2.179</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6424</v>
+        <v>0.9365</v>
       </c>
       <c r="V6" t="n">
         <v>2.2565</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ABELLEIRA MARTINEZ</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5202</v>
+        <v>0.7185</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9557</v>
+        <v>0.2135</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4355</v>
+        <v>0.505</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0473</v>
+        <v>0.3416</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2045</v>
+        <v>-0.0677</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1572</v>
+        <v>0.4093</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4673</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1889</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6563</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5146</v>
+        <v>0.3416</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0156</v>
+        <v>-0.0677</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4991</v>
+        <v>0.4093</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.1543</v>
+        <v>0.1958</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.0921</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9377</v>
+        <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0332</v>
+        <v>0.181</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1559</v>
+        <v>0.2135</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1891</v>
+        <v>-0.0325</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6482</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8249</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9951</v>
+        <v>-0.244</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7168</v>
+        <v>-2.3934</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7217</v>
+        <v>2.1494</v>
       </c>
       <c r="G8" t="n">
         <v>0.4118</v>
@@ -1078,13 +1078,13 @@
         <v>1.7626</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2318</v>
+        <v>0.5193</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0306</v>
+        <v>0.2929</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2013</v>
+        <v>0.2264</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1884</v>
+        <v>-0.887</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4429</v>
+        <v>-1.2217</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2545</v>
+        <v>0.3347</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3189</v>
@@ -1156,13 +1156,13 @@
         <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0653</v>
+        <v>0.236</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1188</v>
+        <v>0.1023</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0535</v>
+        <v>0.1337</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3961</v>
+        <v>-1.2096</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7484</v>
+        <v>0.5984</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6476</v>
+        <v>-1.808</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0981</v>
@@ -1234,13 +1234,13 @@
         <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4871</v>
+        <v>1.6735</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1429</v>
+        <v>1.2039</v>
       </c>
       <c r="U10" t="n">
-        <v>0.63</v>
+        <v>0.4696</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1767</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5733</v>
+        <v>-3.7022</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9755</v>
+        <v>-5.8371</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4022</v>
+        <v>2.1349</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3509</v>
@@ -1312,13 +1312,13 @@
         <v>1.5668</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4031</v>
+        <v>1.2742</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7079</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6952</v>
+        <v>0.4279</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2754</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.777899999999999</v>
+        <v>9.2631</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.459300000000001</v>
+        <v>-1.9743</v>
       </c>
       <c r="F12" t="n">
-        <v>11.2374</v>
+        <v>11.2375</v>
       </c>
       <c r="G12" t="n">
         <v>-8.4268</v>
@@ -1390,16 +1390,16 @@
         <v>15.6676</v>
       </c>
       <c r="S12" t="n">
-        <v>16.9117</v>
+        <v>18.3968</v>
       </c>
       <c r="T12" t="n">
-        <v>10.6098</v>
+        <v>12.0948</v>
       </c>
       <c r="U12" t="n">
-        <v>6.3019</v>
+        <v>6.302099999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1269</v>
+        <v>7.126899999999999</v>
       </c>
       <c r="W12" t="n">
         <v>10.9945</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6355</v>
+        <v>2.7304</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6198</v>
+        <v>2.4151</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0157</v>
+        <v>0.3153</v>
       </c>
       <c r="G13" t="n">
         <v>4.1059</v>
@@ -1468,13 +1468,13 @@
         <v>2.546</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.4865</v>
+        <v>-2.3915</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.8887</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8025</v>
+        <v>-1.5028</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5507</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. SABUGUEIRO ABEIJÓN</t>
+          <t>O. CASTAÑO RUBIANES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9244</v>
+        <v>1.1756</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2677</v>
+        <v>2.6965</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1921</v>
+        <v>-1.5209</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8358</v>
+        <v>4.6935</v>
       </c>
       <c r="H14" t="n">
-        <v>1.488</v>
+        <v>1.4195</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6522</v>
+        <v>3.274</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7411</v>
+        <v>5.6789</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7349</v>
+        <v>1.7538</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.4761</v>
+        <v>3.9251</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5769</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7531</v>
+        <v>-0.3344</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8239</v>
+        <v>-0.6511</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1543</v>
+        <v>1.5668</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1543</v>
+        <v>3.5253</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8491</v>
+        <v>-2.0432</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4734</v>
+        <v>-1.024</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.3225</v>
+        <v>-1.0192</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2166</v>
+        <v>-3.0415</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2166</v>
+        <v>-3.0415</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. CASTAÑO RUBIANES</t>
+          <t>P. SABUGUEIRO ABEIJÓN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7912</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7988</v>
+        <v>-0.984</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0076</v>
+        <v>1.6226</v>
       </c>
       <c r="G15" t="n">
-        <v>4.6935</v>
+        <v>0.8358</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4195</v>
+        <v>1.488</v>
       </c>
       <c r="I15" t="n">
-        <v>3.274</v>
+        <v>-0.6522</v>
       </c>
       <c r="J15" t="n">
-        <v>5.6789</v>
+        <v>-0.7411</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7538</v>
+        <v>0.7349</v>
       </c>
       <c r="L15" t="n">
-        <v>3.9251</v>
+        <v>-1.4761</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9854000000000001</v>
+        <v>1.5769</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3344</v>
+        <v>0.7531</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6511</v>
+        <v>0.8239</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5668</v>
+        <v>2.1543</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.5253</v>
+        <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.4276</v>
+        <v>-1.135</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9216</v>
+        <v>-0.2429</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.506</v>
+        <v>-0.892</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.0415</v>
+        <v>-1.2166</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.0415</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0502</v>
+        <v>-0.0474</v>
       </c>
       <c r="E16" t="n">
         <v>-2.7831</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7329</v>
+        <v>2.7357</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3744</v>
@@ -1702,13 +1702,13 @@
         <v>3.7211</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.163</v>
+        <v>-1.1602</v>
       </c>
       <c r="T16" t="n">
         <v>-0.5652</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5978</v>
+        <v>-0.595</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2754</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. REY MARIÑO</t>
+          <t>P. FERNÁNDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9277</v>
+        <v>-0.7544</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5286</v>
+        <v>-1.1216</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4563</v>
+        <v>0.3672</v>
       </c>
       <c r="G17" t="n">
-        <v>0.783</v>
+        <v>0.2212</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4393</v>
+        <v>-1.9705</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3437</v>
+        <v>2.1917</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4998</v>
+        <v>0.5921</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9799</v>
+        <v>-1.7049</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4802</v>
+        <v>2.297</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2833</v>
+        <v>-0.3709</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5406</v>
+        <v>-0.2656</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8239</v>
+        <v>-0.1053</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9792</v>
+        <v>3.5253</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.531</v>
+        <v>-2.7222</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0288</v>
+        <v>-1.1516</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.5598</v>
+        <v>-1.5706</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.159</v>
+        <v>1.159</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.3756</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.159</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. FERNÁNDEZ CARBALLO</t>
+          <t>D. REY MARIÑO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.515</v>
+        <v>-0.984</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6332</v>
+        <v>0.1192</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1182</v>
+        <v>-1.1032</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2212</v>
+        <v>0.783</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9705</v>
+        <v>0.4393</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1917</v>
+        <v>0.3437</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5921</v>
+        <v>0.4998</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.7049</v>
+        <v>0.9799</v>
       </c>
       <c r="L18" t="n">
-        <v>2.297</v>
+        <v>-0.4802</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3709</v>
+        <v>0.2833</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2656</v>
+        <v>-0.5406</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1053</v>
+        <v>0.8239</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.5253</v>
+        <v>0.9792</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.4828</v>
+        <v>-1.5872</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.6633</v>
+        <v>-0.3805</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.8196</v>
+        <v>-1.2067</v>
       </c>
       <c r="V18" t="n">
-        <v>1.159</v>
+        <v>-1.159</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3756</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2166</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9691</v>
+        <v>-2.0998</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.304</v>
+        <v>-1.8946</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6652</v>
+        <v>-0.2051</v>
       </c>
       <c r="G19" t="n">
         <v>0.335</v>
@@ -1936,13 +1936,13 @@
         <v>2.1543</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.7118</v>
+        <v>-1.8425</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.891</v>
+        <v>-0.4817</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.8208</v>
+        <v>-1.3608</v>
       </c>
       <c r="V19" t="n">
         <v>-1.7673</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2472</v>
+        <v>-3.0932</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.8786</v>
+        <v>-4.674</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6314</v>
+        <v>1.5807</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9954</v>
@@ -2014,13 +2014,13 @@
         <v>2.7419</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6851</v>
+        <v>-1.5311</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3662</v>
+        <v>-1.1616</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3188</v>
+        <v>-0.3695</v>
       </c>
       <c r="V20" t="n">
         <v>0.6083</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4199</v>
+        <v>-3.2972</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.3179</v>
+        <v>-5.0109</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8981</v>
+        <v>1.7137</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1779</v>
@@ -2092,13 +2092,13 @@
         <v>2.1543</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.575</v>
+        <v>-0.4523</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7128</v>
+        <v>-0.4058</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1379</v>
+        <v>-0.0465</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8837</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.778000000000001</v>
+        <v>-5.731400000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-11.2373</v>
+        <v>-11.2374</v>
       </c>
       <c r="F22" t="n">
-        <v>3.4593</v>
+        <v>5.506</v>
       </c>
       <c r="G22" t="n">
         <v>8.4267</v>
@@ -2155,7 +2155,7 @@
         <v>1.5618</v>
       </c>
       <c r="N22" t="n">
-        <v>0.04160000000000008</v>
+        <v>0.04160000000000025</v>
       </c>
       <c r="O22" t="n">
         <v>1.5203</v>
@@ -2170,13 +2170,13 @@
         <v>23.5017</v>
       </c>
       <c r="S22" t="n">
-        <v>-16.9119</v>
+        <v>-14.8652</v>
       </c>
       <c r="T22" t="n">
-        <v>-6.3019</v>
+        <v>-6.302</v>
       </c>
       <c r="U22" t="n">
-        <v>-10.6099</v>
+        <v>-8.5631</v>
       </c>
       <c r="V22" t="n">
         <v>-7.1269</v>
